--- a/stories/arbres/ATOM-EMO.LEX.008-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tess est dans le salon avec papa. Elle fait tomber un livre. Ses joues chauffent. Elle dit : je suis gênée. Papa écoute. Papa dit : une erreur, ce n'est pas toi tout entier. On dit. On répare. Tess dit : j'ai fait tomber. Elle ramasse le livre. Elle le pose. Elle répare. Papa dit : merci.</t>
+          <t>Tess est dans le salon avec papa. Elle fait tomber un livre. Ses joues chauffent. Je suis gênée. Papa écoute. Une erreur, ce n'est pas toi tout entier. On dit. On répare. J'ai fait tomber. Elle ramasse le livre. Elle le pose. Elle répare. Merci.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Tess est dans le salon avec papa. Elle fait tomber un livre. Ses joues chauffent.
+narrateur|Je suis gênée. Papa écoute.
+papa|Une erreur, ce n'est pas toi tout entier. On dit. On répare.
+enfant-m|J'ai fait tomber. Elle ramasse le livre. Elle le pose. Elle répare.
+papa|Merci.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1467,6 +1492,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Tess a fait tomber le livre. Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1491,7 +1521,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tess a dit : je suis gênée. Elle a réparé l'erreur.</t>
+          <t>Tess Je suis gênée. Elle a réparé l'erreur.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1633,6 +1663,12 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Tess
+enfant-f|Je suis gênée. Elle a réparé l'erreur.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1827,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa ouvre le livre. Tess s'assoit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1994,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2034,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.008-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 papa|Merci.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Tess a fait tomber le livre. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1676,7 @@
 enfant-f|Je suis gênée. Elle a réparé l'erreur.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1832,6 +1840,7 @@
           <t>narrateur|Papa ouvre le livre. Tess s'assoit.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1999,6 +2008,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2017,7 +2027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2051,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2242,6 +2266,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.008-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tess est gênée et elle répare</t>
+          <t>Nina est gênée et elle répare</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nina fait tomber un livre. Elle dit qu'elle est gênée. Elle ramasse. Elle répare. Papa ouvre le livre.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tess est dans le salon avec papa. Elle fait tomber un livre. Ses joues chauffent. Je suis gênée. Papa écoute. Une erreur, ce n'est pas toi tout entier. On dit. On répare. J'ai fait tomber. Elle ramasse le livre. Elle le pose. Elle répare. Merci.</t>
+          <t>Le doudou de Nina attend dans le fauteuil. Une oreille du doudou dépasse du coussin. Le tissu du doudou est un peu usé, tout doux. La lampe du salon fait un rond sur le tapis. Le tapis est épais, un peu beige. Une chaussette rayée attend près du pied de la table. Sur la table basse, une pile de livres. Le plus grand a une couverture bleue. Un rideau bougé laisse un filet de lumière. Nina, on range les livres avant l'histoire ? Oui, papa. Je les mets près du fauteuil. Tout doux. Le doudou attend déjà. En ce moment, Nina est dans le salon avec papa. Elle prend le livre bleu. Le livre glisse. Il tombe sur le tapis, tout mou. Ses joues chauffent. Je suis gênée. Je t'écoute. Une erreur, ce n'est pas toi tout entier. On dit. On répare. J'ai fait tomber. Merci d'avoir dit. Nina ramasse le livre. Elle le pose sur la table basse. Elle répare. Bravo, Nina. C'est du bon travail. J'ai dit. J'ai réparé. L'erreur n'est pas toi. Tes joues sont moins chaudes, maintenant ? Oui, papa. Le doudou n'a pas bougé. Son oreille dépasse encore. On ouvre le livre, ensemble ? Oui. Une page, tout doux. Le rond de la lampe reste sur le tapis. Tu as dit. Tu as réparé. Le doudou m'attendait.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1324,51 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Tess est dans le salon avec papa. Elle fait tomber un livre. Ses joues chauffent.
-narrateur|Je suis gênée. Papa écoute.
-papa|Une erreur, ce n'est pas toi tout entier. On dit. On répare.
-enfant-m|J'ai fait tomber. Elle ramasse le livre. Elle le pose. Elle répare.
-papa|Merci.</t>
+          <t>narrateur|Le doudou de Nina attend dans le fauteuil.
+narrateur|Une oreille du doudou dépasse du coussin.
+narrateur|Le tissu du doudou est un peu usé, tout doux.
+narrateur|La lampe du salon fait un rond sur le tapis.
+narrateur|Le tapis est épais, un peu beige.
+narrateur|Une chaussette rayée attend près du pied de la table.
+narrateur|Sur la table basse, une pile de livres.
+narrateur|Le plus grand a une couverture bleue.
+narrateur|Un rideau bougé laisse un filet de lumière.
+papa|Nina, on range les livres avant l'histoire ?
+enfant-f|Oui, papa.
+enfant-f|Je les mets près du fauteuil.
+papa|Tout doux.
+papa|Le doudou attend déjà.
+narrateur|En ce moment, Nina est dans le salon avec papa.
+narrateur|Elle prend le livre bleu.
+narrateur|Le livre glisse.
+narrateur|Il tombe sur le tapis, tout mou.
+narrateur|Ses joues chauffent.
+enfant-f|Je suis gênée.
+papa|Je t'écoute.
+papa|Une erreur, ce n'est pas toi tout entier.
+papa|On dit.
+papa|On répare.
+enfant-f|J'ai fait tomber.
+papa|Merci d'avoir dit.
+narrateur|Nina ramasse le livre.
+narrateur|Elle le pose sur la table basse.
+narrateur|Elle répare.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|J'ai dit.
+enfant-f|J'ai réparé.
+papa|L'erreur n'est pas toi.
+papa|Tes joues sont moins chaudes, maintenant ?
+enfant-f|Oui, papa.
+narrateur|Le doudou n'a pas bougé.
+narrateur|Son oreille dépasse encore.
+papa|On ouvre le livre, ensemble ?
+enfant-f|Oui.
+enfant-f|Une page, tout doux.
+narrateur|Le rond de la lampe reste sur le tapis.
+papa|Tu as dit.
+papa|Tu as réparé.
+enfant-f|Le doudou m'attendait.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1344,7 +1396,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Tess a fait tomber le livre. Que fait-elle ?</t>
+          <t>Nina a fait tomber le livre. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,7 +1552,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Tess a fait tomber le livre. Que fait-elle ?</t>
+          <t>narrateur|Nina a fait tomber le livre.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1528,7 +1581,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tess Je suis gênée. Elle a réparé l'erreur.</t>
+          <t>Nina a nommé : gêné. Elle a réparé l'erreur. Je suis gênée. J'ai fait tomber. J'ai réparé. Oui. Tu as dit. Tu as ramassé. Bravo. C'est du bon travail. Le livre bleu est de nouveau sur la table. Une erreur, ce n'est pas toi tout entier. On dit. On répare. Oui. C'est le bon geste. La chaussette rayée n'a pas bougé.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,8 +1725,23 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Tess
-enfant-f|Je suis gênée. Elle a réparé l'erreur.</t>
+          <t>narrateur|Nina a nommé : gêné.
+narrateur|Elle a réparé l'erreur.
+enfant-f|Je suis gênée.
+enfant-f|J'ai fait tomber.
+enfant-f|J'ai réparé.
+papa|Oui.
+papa|Tu as dit.
+papa|Tu as ramassé.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Le livre bleu est de nouveau sur la table.
+papa|Une erreur, ce n'est pas toi tout entier.
+enfant-f|On dit.
+enfant-f|On répare.
+papa|Oui.
+papa|C'est le bon geste.
+narrateur|La chaussette rayée n'a pas bougé.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1701,7 +1769,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa ouvre le livre. Tess s'assoit.</t>
+          <t>Papa ouvre le livre. Nina s'assoit. Tu t'assois près du doudou ? Oui. Il m'attendait. On lit la première page. J'étais gênée. Et tu as réparé. Bravo. Les pages sentent le papier. Le tapis est doux sous les genoux. L'erreur n'est pas toi. Le livre est rangé. Oui. On peut lire, maintenant. Le rideau redevient immobile. Tu prends le doudou sur tes genoux ? Oui. Il est chaud. On tourne la page ? Oui. Une image bleue. Comme la couverture. Le filet de lumière reste sur le tapis. Tu as dit l'erreur. Tu as réparé. Maintenant, on lit. L'oreille du doudou dépasse encore. On reste ici un peu ? Oui. Près de toi.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1837,7 +1905,37 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa ouvre le livre. Tess s'assoit.</t>
+          <t>narrateur|Papa ouvre le livre.
+narrateur|Nina s'assoit.
+papa|Tu t'assois près du doudou ?
+enfant-f|Oui.
+enfant-f|Il m'attendait.
+papa|On lit la première page.
+enfant-f|J'étais gênée.
+papa|Et tu as réparé.
+papa|Bravo.
+narrateur|Les pages sentent le papier.
+narrateur|Le tapis est doux sous les genoux.
+papa|L'erreur n'est pas toi.
+enfant-f|Le livre est rangé.
+papa|Oui.
+papa|On peut lire, maintenant.
+narrateur|Le rideau redevient immobile.
+papa|Tu prends le doudou sur tes genoux ?
+enfant-f|Oui.
+enfant-f|Il est chaud.
+papa|On tourne la page ?
+enfant-f|Oui.
+enfant-f|Une image bleue.
+papa|Comme la couverture.
+narrateur|Le filet de lumière reste sur le tapis.
+papa|Tu as dit l'erreur.
+papa|Tu as réparé.
+enfant-f|Maintenant, on lit.
+narrateur|L'oreille du doudou dépasse encore.
+papa|On reste ici un peu ?
+enfant-f|Oui.
+enfant-f|Près de toi.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1865,7 +1963,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'étais gênée. J'ai dit. J'ai réparé. Bravo, Nina. Tu as fait du bon travail. Le doudou reste dans le fauteuil. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2005,7 +2103,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'étais gênée.
+enfant-f|J'ai dit.
+enfant-f|J'ai réparé.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Le doudou reste dans le fauteuil.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2027,7 +2131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2065,6 +2169,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.008-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-05.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le doudou de Nina attend dans le fauteuil. Une oreille du doudou dépasse du coussin. Le tissu du doudou est un peu usé, tout doux. La lampe du salon fait un rond sur le tapis. Le tapis est épais, un peu beige. Une chaussette rayée attend près du pied de la table. Sur la table basse, une pile de livres. Le plus grand a une couverture bleue. Un rideau bougé laisse un filet de lumière. Nina, on range les livres avant l'histoire ? Oui, papa. Je les mets près du fauteuil. Tout doux. Le doudou attend déjà. En ce moment, Nina est dans le salon avec papa. Elle prend le livre bleu. Le livre glisse. Il tombe sur le tapis, tout mou. Ses joues chauffent. Je suis gênée. Je t'écoute. Une erreur, ce n'est pas toi tout entier. On dit. On répare. J'ai fait tomber. Merci d'avoir dit. Nina ramasse le livre. Elle le pose sur la table basse. Elle répare. Bravo, Nina. C'est du bon travail. J'ai dit. J'ai réparé. L'erreur n'est pas toi. Tes joues sont moins chaudes, maintenant ? Oui, papa. Le doudou n'a pas bougé. Son oreille dépasse encore. On ouvre le livre, ensemble ? Oui. Une page, tout doux. Le rond de la lampe reste sur le tapis. Tu as dit. Tu as réparé. Le doudou m'attendait.</t>
+          <t>Le doudou de Nina attend dans le fauteuil. Une oreille du doudou dépasse du coussin. Le tissu du doudou est un peu usé, tout doux. La lampe du salon fait un rond sur le tapis. Le tapis est épais, un peu beige. Une chaussette rayée attend près du pied de la table. Sur la table basse, une pile de livres. Le plus grand a une couverture bleue. Un rideau bougé laisse un filet de lumière. Nina, on range les livres avant l'histoire ? Oui, papa. Je les mets près du fauteuil. Tout doux. Le doudou attend déjà. En ce moment, Nina est dans le salon avec papa. Elle prend le livre bleu. Le livre glisse. Il tombe sur le tapis, tout mou. Ses joues chauffent. Je suis gênée. Je t'écoute. Une erreur, ce n'est pas toi tout entier. On dit. On répare. J'ai fait tomber. Merci d'avoir dit. Nina ramasse le livre. Elle le pose sur la table basse. Elle répare. Bravo, Nina. J'ai dit. J'ai réparé. L'erreur n'est pas toi. Tes joues sont moins chaudes, maintenant ? Oui, papa. Le doudou n'a pas bougé. Son oreille dépasse encore. On ouvre le livre, ensemble ? Oui. Une page, tout doux. Le rond de la lampe reste sur le tapis. Tu as dit. Tu as réparé. Le doudou m'attendait.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tess est dans le salon avec papa. Elle fait tomber un livre. Ses joues chauffent. Elle dit : je suis &lt;emphasis level="moderate"&gt;gêné&lt;/emphasis&gt;e. Papa écoute. Papa dit : une erreur, ce n'est pas toi tout entier. On dit. On répare. Tess dit : j'ai fait tomber. Elle ramasse le livre. Elle le pose. Elle répare. Papa dit : merci.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le doudou de Nina attend dans le fauteuil. Une oreille du doudou dépasse du coussin. Le tissu du doudou est un peu usé, tout doux. La lampe du salon fait un rond sur le tapis. Le tapis est épais, un peu beige. Une chaussette rayée attend près du pied de la table. Sur la table basse, une pile de livres. Le plus grand a une couverture bleue. Un rideau bougé laisse un filet de lumière. Nina, on range les livres avant l'histoire ? Oui, papa. Je les mets près du fauteuil. Tout doux. Le doudou attend déjà. En ce moment, Nina est dans le salon avec papa. Elle prend le livre bleu. Le livre glisse. Il tombe sur le tapis, tout mou. Ses joues chauffent. Je suis gênée. Je t'écoute. Une erreur, ce n'est pas toi tout entier. On dit. On répare. J'ai fait tomber. Merci d'avoir dit. Nina ramasse le livre. Elle le pose sur la table basse. Elle répare. Bravo, Nina. J'ai dit. J'ai réparé. L'erreur n'est pas toi. Tes joues sont moins chaudes, maintenant ? Oui, papa. Le doudou n'a pas bougé. Son oreille dépasse encore. On ouvre le livre, ensemble ? Oui. Une page, tout doux. Le rond de la lampe reste sur le tapis. Tu as dit. Tu as réparé. Le doudou m'attendait.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1354,7 +1354,6 @@
 narrateur|Elle le pose sur la table basse.
 narrateur|Elle répare.
 papa|Bravo, Nina.
-papa|C'est du bon travail.
 enfant-f|J'ai dit.
 enfant-f|J'ai réparé.
 papa|L'erreur n'est pas toi.
@@ -1371,7 +1370,6 @@
 enfant-f|Le doudou m'attendait.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1401,7 +1399,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tess a fait tomber le livre. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a fait tomber le livre. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1556,7 +1554,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1581,12 +1578,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina a nommé : gêné. Elle a réparé l'erreur. Je suis gênée. J'ai fait tomber. J'ai réparé. Oui. Tu as dit. Tu as ramassé. Bravo. C'est du bon travail. Le livre bleu est de nouveau sur la table. Une erreur, ce n'est pas toi tout entier. On dit. On répare. Oui. C'est le bon geste. La chaussette rayée n'a pas bougé.</t>
+          <t>Nina a nommé : gêné. Elle a réparé l'erreur. Je suis gênée. J'ai fait tomber. J'ai réparé. Oui. Tu as dit. Tu as ramassé. Bravo. Le livre bleu est de nouveau sur la table. Une erreur, ce n'est pas toi tout entier. On dit. On répare. Oui. C'est le bon geste. La chaussette rayée n'a pas bougé.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tess a dit : je suis &lt;emphasis level="moderate"&gt;gêné&lt;/emphasis&gt;e. Elle a réparé l'erreur.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a nommé : gêné. Elle a réparé l'erreur. Je suis gênée. J'ai fait tomber. J'ai réparé. Oui. Tu as dit. Tu as ramassé. Bravo. Le livre bleu est de nouveau sur la table. Une erreur, ce n'est pas toi tout entier. On dit. On répare. Oui. C'est le bon geste. La chaussette rayée n'a pas bougé.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1734,7 +1731,6 @@
 papa|Tu as dit.
 papa|Tu as ramassé.
 papa|Bravo.
-papa|C'est du bon travail.
 narrateur|Le livre bleu est de nouveau sur la table.
 papa|Une erreur, ce n'est pas toi tout entier.
 enfant-f|On dit.
@@ -1744,7 +1740,6 @@
 narrateur|La chaussette rayée n'a pas bougé.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1774,7 +1769,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa ouvre le livre. Tess s'assoit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa ouvre le livre. Nina s'assoit. Tu t'assois près du doudou ? Oui. Il m'attendait. On lit la première page. J'étais gênée. Et tu as réparé. Bravo. Les pages sentent le papier. Le tapis est doux sous les genoux. L'erreur n'est pas toi. Le livre est rangé. Oui. On peut lire, maintenant. Le rideau redevient immobile. Tu prends le doudou sur tes genoux ? Oui. Il est chaud. On tourne la page ? Oui. Une image bleue. Comme la couverture. Le filet de lumière reste sur le tapis. Tu as dit l'erreur. Tu as réparé. Maintenant, on lit. L'oreille du doudou dépasse encore. On reste ici un peu ? Oui. Près de toi.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1938,7 +1933,6 @@
 enfant-f|Près de toi.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1963,12 +1957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'étais gênée. J'ai dit. J'ai réparé. Bravo, Nina. Tu as fait du bon travail. Le doudou reste dans le fauteuil. L'histoire est finie.</t>
+          <t>J'étais gênée. J'ai dit. J'ai réparé. Bravo, Nina. Le doudou reste dans le fauteuil.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'étais gênée. J'ai dit. J'ai réparé. Bravo, Nina. Le doudou reste dans le fauteuil.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2107,12 +2101,9 @@
 enfant-f|J'ai dit.
 enfant-f|J'ai réparé.
 papa|Bravo, Nina.
-papa|Tu as fait du bon travail.
-narrateur|Le doudou reste dans le fauteuil.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le doudou reste dans le fauteuil.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2131,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2176,6 +2167,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.008-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-05.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tess, papa</t>
+          <t>Nina, papa</t>
         </is>
       </c>
     </row>
